--- a/rapporten/prijsrapport-2026-04-27.xlsx
+++ b/rapporten/prijsrapport-2026-04-27.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="133">
   <si>
     <t>Product</t>
   </si>
@@ -388,142 +388,28 @@
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
-  </si>
-  <si>
-    <t>6291012005082</t>
-  </si>
-  <si>
-    <t>Street Looks Uptown Babe eau de parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658340270</t>
-  </si>
-  <si>
-    <t>Real Time Queen of Space parfum - Eau de parfum voor elegante vrouwen - 100ml</t>
-  </si>
-  <si>
-    <t>8715658360896</t>
-  </si>
-  <si>
-    <t>Real Time - Blue Touch - Eau De Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658350446</t>
-  </si>
-  <si>
-    <t>Linn Young "Je Suis Sure Et Certaine" Eau de parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658400295</t>
-  </si>
-  <si>
-    <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350033</t>
-  </si>
-  <si>
-    <t>Real Time - Nuit Charmante - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360001</t>
-  </si>
-  <si>
-    <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360971</t>
-  </si>
-  <si>
-    <t>Omerta - Conclude Oud Orient Perfection - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370550</t>
-  </si>
-  <si>
-    <t>Street Looks - Wild Challenge - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658330004</t>
-  </si>
-  <si>
-    <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370574</t>
-  </si>
-  <si>
-    <t>Vibezz-French Marine-Eau de Toilette For Him-100ml</t>
-  </si>
-  <si>
-    <t>7640158819234</t>
-  </si>
-  <si>
-    <t>Omerta - Express sensualite Captive - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658999027</t>
-  </si>
-  <si>
-    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
-  </si>
-  <si>
-    <t>7640158819173</t>
-  </si>
-  <si>
-    <t>Creation Lamis Diable Bleu parfum - Oriëntaalse en houtige eau de parfum voor dames</t>
-  </si>
-  <si>
-    <t>5414666001366</t>
-  </si>
-  <si>
-    <t>Real Time - Smart Lady For Women - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360995</t>
-  </si>
-  <si>
-    <t>Real Time - Night Blue Mission Pour Homme - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658002772</t>
-  </si>
-  <si>
-    <t>Omerta - Candy Puff - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380801</t>
-  </si>
-  <si>
-    <t>Hello Kitty Delicate Flower Eau de Parfum voor Kinderen 50ml</t>
-  </si>
-  <si>
-    <t>7640158816875</t>
-  </si>
-  <si>
-    <t>Omerta Oh My Dear L'extase parfum - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380245</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Giftset - Delicate Flower - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>7640158816950</t>
-  </si>
-  <si>
-    <t>Creation Lamis Golden Wave for Men Giftset</t>
-  </si>
-  <si>
-    <t>6291012002661</t>
-  </si>
-  <si>
-    <t>Real Time Loveliness La Passione - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360759</t>
+    <t>Hello Kitty - Giftset - Rainbow - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055493426</t>
+  </si>
+  <si>
+    <t>Vibezz Il Capitano - Eau de Toilette voor heren - 100ml</t>
+  </si>
+  <si>
+    <t>7640158819241</t>
+  </si>
+  <si>
+    <t>Omerta - Fair Fight - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658997924</t>
+  </si>
+  <si>
+    <t>Bubble Bliss Parfum Giftbag Glimmering Grace EDP voor meisjes 50ml</t>
+  </si>
+  <si>
+    <t>8721055494324</t>
   </si>
 </sst>
 </file>
@@ -915,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2418,19 +2304,19 @@
         <v>128</v>
       </c>
       <c r="C58" s="1">
-        <v>14.82</v>
+        <v>14.59</v>
       </c>
       <c r="D58" s="1">
-        <v>14.65</v>
+        <v>14.49</v>
       </c>
       <c r="E58" s="1">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="F58" t="s">
         <v>124</v>
       </c>
       <c r="G58" s="1">
-        <v>14.65</v>
+        <v>14.49</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -2444,19 +2330,19 @@
         <v>130</v>
       </c>
       <c r="C59" s="1">
-        <v>14.79</v>
+        <v>14.59</v>
       </c>
       <c r="D59" s="1">
-        <v>14.65</v>
+        <v>14.49</v>
       </c>
       <c r="E59" s="1">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F59" t="s">
         <v>124</v>
       </c>
       <c r="G59" s="1">
-        <v>14.65</v>
+        <v>14.49</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -2470,515 +2356,21 @@
         <v>132</v>
       </c>
       <c r="C60" s="1">
-        <v>14.79</v>
+        <v>13.59</v>
       </c>
       <c r="D60" s="1">
-        <v>14.65</v>
+        <v>13.53</v>
       </c>
       <c r="E60" s="1">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="F60" t="s">
         <v>124</v>
       </c>
       <c r="G60" s="1">
-        <v>14.65</v>
+        <v>13.53</v>
       </c>
       <c r="H60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>133</v>
-      </c>
-      <c r="B61" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="1">
-        <v>14.79</v>
-      </c>
-      <c r="D61" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0.14</v>
-      </c>
-      <c r="F61" t="s">
-        <v>124</v>
-      </c>
-      <c r="G61" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>135</v>
-      </c>
-      <c r="B62" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="1">
-        <v>14.79</v>
-      </c>
-      <c r="D62" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.14</v>
-      </c>
-      <c r="F62" t="s">
-        <v>124</v>
-      </c>
-      <c r="G62" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>137</v>
-      </c>
-      <c r="B63" t="s">
-        <v>138</v>
-      </c>
-      <c r="C63" s="1">
-        <v>14.79</v>
-      </c>
-      <c r="D63" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0.14</v>
-      </c>
-      <c r="F63" t="s">
-        <v>124</v>
-      </c>
-      <c r="G63" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>139</v>
-      </c>
-      <c r="B64" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D64" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>124</v>
-      </c>
-      <c r="G64" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>141</v>
-      </c>
-      <c r="B65" t="s">
-        <v>142</v>
-      </c>
-      <c r="C65" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D65" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F65" t="s">
-        <v>124</v>
-      </c>
-      <c r="G65" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>143</v>
-      </c>
-      <c r="B66" t="s">
-        <v>144</v>
-      </c>
-      <c r="C66" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D66" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F66" t="s">
-        <v>124</v>
-      </c>
-      <c r="G66" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" t="s">
-        <v>146</v>
-      </c>
-      <c r="C67" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D67" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F67" t="s">
-        <v>124</v>
-      </c>
-      <c r="G67" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>147</v>
-      </c>
-      <c r="B68" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" s="1">
-        <v>14.59</v>
-      </c>
-      <c r="D68" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F68" t="s">
-        <v>124</v>
-      </c>
-      <c r="G68" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="H68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" t="s">
-        <v>150</v>
-      </c>
-      <c r="C69" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D69" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F69" t="s">
-        <v>124</v>
-      </c>
-      <c r="G69" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>151</v>
-      </c>
-      <c r="B70" t="s">
-        <v>152</v>
-      </c>
-      <c r="C70" s="1">
-        <v>14.59</v>
-      </c>
-      <c r="D70" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F70" t="s">
-        <v>124</v>
-      </c>
-      <c r="G70" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="H70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>153</v>
-      </c>
-      <c r="B71" t="s">
-        <v>154</v>
-      </c>
-      <c r="C71" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D71" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F71" t="s">
-        <v>124</v>
-      </c>
-      <c r="G71" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>155</v>
-      </c>
-      <c r="B72" t="s">
-        <v>156</v>
-      </c>
-      <c r="C72" s="1">
-        <v>14.59</v>
-      </c>
-      <c r="D72" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F72" t="s">
-        <v>124</v>
-      </c>
-      <c r="G72" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="H72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>157</v>
-      </c>
-      <c r="B73" t="s">
-        <v>158</v>
-      </c>
-      <c r="C73" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D73" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F73" t="s">
-        <v>124</v>
-      </c>
-      <c r="G73" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>159</v>
-      </c>
-      <c r="B74" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="1">
-        <v>14.59</v>
-      </c>
-      <c r="D74" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F74" t="s">
-        <v>124</v>
-      </c>
-      <c r="G74" s="1">
-        <v>14.49</v>
-      </c>
-      <c r="H74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>161</v>
-      </c>
-      <c r="B75" t="s">
-        <v>162</v>
-      </c>
-      <c r="C75" s="1">
-        <v>13.3</v>
-      </c>
-      <c r="D75" s="1">
-        <v>13.21</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F75" t="s">
-        <v>124</v>
-      </c>
-      <c r="G75" s="1">
-        <v>13.21</v>
-      </c>
-      <c r="H75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>163</v>
-      </c>
-      <c r="B76" t="s">
-        <v>164</v>
-      </c>
-      <c r="C76" s="1">
-        <v>12.92</v>
-      </c>
-      <c r="D76" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0.07</v>
-      </c>
-      <c r="F76" t="s">
-        <v>124</v>
-      </c>
-      <c r="G76" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="H76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" t="s">
-        <v>166</v>
-      </c>
-      <c r="C77" s="1">
-        <v>12.99</v>
-      </c>
-      <c r="D77" s="1">
-        <v>12.92</v>
-      </c>
-      <c r="E77" s="1">
-        <v>0.07</v>
-      </c>
-      <c r="F77" t="s">
-        <v>124</v>
-      </c>
-      <c r="G77" s="1">
-        <v>12.92</v>
-      </c>
-      <c r="H77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>167</v>
-      </c>
-      <c r="B78" t="s">
-        <v>168</v>
-      </c>
-      <c r="C78" s="1">
-        <v>12.89</v>
-      </c>
-      <c r="D78" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F78" t="s">
-        <v>124</v>
-      </c>
-      <c r="G78" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="H78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>169</v>
-      </c>
-      <c r="B79" t="s">
-        <v>170</v>
-      </c>
-      <c r="C79" s="1">
-        <v>12.79</v>
-      </c>
-      <c r="D79" s="1">
-        <v>12.78</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="F79" t="s">
-        <v>124</v>
-      </c>
-      <c r="G79" s="1">
-        <v>12.78</v>
-      </c>
-      <c r="H79" t="s">
         <v>11</v>
       </c>
     </row>
